--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713491</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713475</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713456</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115947223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,8 +1396,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115947405</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133713505</v>
+        <v>135749597</v>
       </c>
       <c r="B2" t="n">
-        <v>58563</v>
+        <v>57865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102987</v>
+        <v>100100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalhem, Vg</t>
+          <t>ekliden1 Mollaryd, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>383131</v>
+        <v>383175</v>
       </c>
       <c r="R2" t="n">
-        <v>6419683</v>
+        <v>6419842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>04:20</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,49 +784,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Epp Laas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eskil Friberg</t>
+          <t>Epp Laas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133713505</t>
+          <t>https://artportalen.se/Sighting/135749597</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133713491</v>
+        <v>133713505</v>
       </c>
       <c r="B3" t="n">
-        <v>58485</v>
+        <v>58563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>102987</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +838,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -851,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>383124</v>
+        <v>383131</v>
       </c>
       <c r="R3" t="n">
-        <v>6419712</v>
+        <v>6419683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,16 +919,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133713491</t>
+          <t>https://artportalen.se/Sighting/133713505</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133713475</v>
+        <v>133713491</v>
       </c>
       <c r="B4" t="n">
-        <v>58461</v>
+        <v>58485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>383199</v>
+        <v>383124</v>
       </c>
       <c r="R4" t="n">
-        <v>6419856</v>
+        <v>6419712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,50 +1043,50 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133713475</t>
+          <t>https://artportalen.se/Sighting/133713491</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133713456</v>
+        <v>133713475</v>
       </c>
       <c r="B5" t="n">
-        <v>58375</v>
+        <v>58461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1099,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>383115</v>
+        <v>383199</v>
       </c>
       <c r="R5" t="n">
-        <v>6419660</v>
+        <v>6419856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1170,63 +1167,63 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133713456</t>
+          <t>https://artportalen.se/Sighting/133713475</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115947223</v>
+        <v>133713456</v>
       </c>
       <c r="B6" t="n">
-        <v>58636</v>
+        <v>58375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ekliden1 Mollaryd, Vg</t>
+          <t>Dalhem, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>383175</v>
+        <v>383115</v>
       </c>
       <c r="R6" t="n">
-        <v>6419842</v>
+        <v>6419660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,12 +1250,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,54 +1280,54 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Epp Laas</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Epp Laas</t>
+          <t>Eskil Friberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115947223</t>
+          <t>https://artportalen.se/Sighting/133713456</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115947405</v>
+        <v>115947223</v>
       </c>
       <c r="B7" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1397,6 +1404,120 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115947223</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115947405</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ekliden1 Mollaryd, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>383175</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6419842</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Herrljunga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Molla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Epp Laas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Epp Laas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115947405</t>
         </is>
@@ -1410,6 +1531,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
